--- a/ValueSet-ng-results-specimen-collection-method-vs.xlsx
+++ b/ValueSet-ng-results-specimen-collection-method-vs.xlsx
@@ -75,7 +75,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T13:22:49+01:00</t>
+    <t>2026-08-17T07:55:48+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ng-results-specimen-collection-method-vs.xlsx
+++ b/ValueSet-ng-results-specimen-collection-method-vs.xlsx
@@ -75,7 +75,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T07:55:48+01:00</t>
+    <t>2026-08-17T13:27:53+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ng-results-specimen-collection-method-vs.xlsx
+++ b/ValueSet-ng-results-specimen-collection-method-vs.xlsx
@@ -75,7 +75,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T13:27:53+01:00</t>
+    <t>2026-08-17T16:10:29+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ng-results-specimen-collection-method-vs.xlsx
+++ b/ValueSet-ng-results-specimen-collection-method-vs.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="47">
   <si>
     <t>Property</t>
   </si>
@@ -75,7 +75,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T16:10:29+01:00</t>
+    <t>2026-08-18T06:18:50+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,13 +87,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>NDHI (https://digitalhealth.gov.ng, emeka2015@gmail.com)</t>
-  </si>
-  <si>
-    <t>Nigeria Digital in Health Initiative. (lekeojewale@gmail.com(Work))</t>
-  </si>
-  <si>
-    <t>Nigeria Digital in Health Initiative. (emeka2015@gmail.com(Work))</t>
+    <t>NDHI (https://digitalhealth.gov.ng)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -302,7 +296,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -399,56 +393,40 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>25</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B17" t="s" s="2">
+      <c r="B16" t="s" s="2">
         <v>30</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -470,37 +448,37 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>33</v>
       </c>
-      <c r="C1" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>35</v>
-      </c>
       <c r="C2" t="s" s="2">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>37</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -522,37 +500,37 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>33</v>
       </c>
-      <c r="C1" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>35</v>
-      </c>
       <c r="C2" t="s" s="2">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>37</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -574,37 +552,37 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>33</v>
       </c>
-      <c r="C1" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
+      <c r="C2" t="s" s="2">
         <v>34</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="C2" t="s" s="2">
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
         <v>36</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
+      <c r="B4" t="s" s="2">
         <v>37</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -626,18 +604,122 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>33</v>
       </c>
+      <c r="C2" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>31</v>
+      </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>35</v>
+        <v>32</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>33</v>
       </c>
       <c r="C2" t="s" s="2">
         <v>40</v>
@@ -645,26 +727,26 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -678,18 +760,18 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>35</v>
       </c>
       <c r="C2" t="s" s="2">
         <v>41</v>
@@ -697,26 +779,26 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -730,18 +812,18 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>35</v>
       </c>
       <c r="C2" t="s" s="2">
         <v>42</v>
@@ -749,26 +831,26 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -782,18 +864,18 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>35</v>
       </c>
       <c r="C2" t="s" s="2">
         <v>43</v>
@@ -801,26 +883,26 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -834,18 +916,18 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>35</v>
       </c>
       <c r="C2" t="s" s="2">
         <v>44</v>
@@ -853,123 +935,19 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>33</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>33</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>39</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ValueSet-ng-results-specimen-collection-method-vs.xlsx
+++ b/ValueSet-ng-results-specimen-collection-method-vs.xlsx
@@ -75,7 +75,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T06:18:50+01:00</t>
+    <t>2026-08-18T15:57:17+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ng-results-specimen-collection-method-vs.xlsx
+++ b/ValueSet-ng-results-specimen-collection-method-vs.xlsx
@@ -75,7 +75,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T15:57:17+01:00</t>
+    <t>2026-08-18T16:47:52+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
